--- a/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.94784942299811</v>
+        <v>45.55580739752585</v>
       </c>
       <c r="M2" t="n">
-        <v>101.2121306972057</v>
+        <v>99.41611275114525</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00960267999706</v>
+        <v>88.04449399340598</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88960365155118</v>
+        <v>45.91437771398322</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228714831612412</v>
+        <v>2.228785540114587</v>
       </c>
       <c r="E3" t="n">
-        <v>5.683177103383743</v>
+        <v>5.699200340445213</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429049438708042</v>
+        <v>0.7429285133715291</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95971990239438</v>
+        <v>33.9679610778542</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17362741805699</v>
+        <v>34.17471161509033</v>
       </c>
       <c r="I3" t="n">
-        <v>6.578302581486205</v>
+        <v>6.587603697958063</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643155899192526</v>
+        <v>4.643303208572057</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99039732000294</v>
+        <v>11.95550600659401</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88387002752827</v>
+        <v>48.89366091557041</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638709990824</v>
+        <v>106.7635446361477</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.17826549380175</v>
+        <v>87.23409869200458</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69683273138355</v>
+        <v>42.74342512843387</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189053339270992</v>
+        <v>2.190268511661727</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497613339520437</v>
+        <v>6.517577168229649</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444653858704876</v>
+        <v>0.7444902136182925</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35538364917746</v>
+        <v>33.38093962613836</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24540775004242</v>
+        <v>34.24654982644145</v>
       </c>
       <c r="I4" t="n">
-        <v>5.493433368229393</v>
+        <v>5.501209510800784</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652908661690548</v>
+        <v>4.653063835114328</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82173450619826</v>
+        <v>12.7659013079954</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29870213515468</v>
+        <v>44.30768457196077</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81726937273649</v>
+        <v>99.81701100839005</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.11549181692405</v>
+        <v>86.2406831205938</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48671889366021</v>
+        <v>42.60391682473734</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137504266486009</v>
+        <v>2.142368017054823</v>
       </c>
       <c r="E5" t="n">
-        <v>7.108935086186016</v>
+        <v>7.140452897728013</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457869091869848</v>
+        <v>0.7458117304723393</v>
       </c>
       <c r="G5" t="n">
-        <v>32.56991210828066</v>
+        <v>32.65090880570615</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30619782260129</v>
+        <v>34.30733960172761</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585987441764437</v>
+        <v>4.592478752452753</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661168182418654</v>
+        <v>4.661323315452121</v>
       </c>
       <c r="K5" t="n">
-        <v>13.88450818307595</v>
+        <v>13.75931687940621</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47617755192413</v>
+        <v>43.48395492055644</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84740462866029</v>
+        <v>99.84718862469998</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.90721455782882</v>
+        <v>85.15490022008355</v>
       </c>
       <c r="C6" t="n">
-        <v>41.99080381128952</v>
+        <v>42.23160282162507</v>
       </c>
       <c r="D6" t="n">
-        <v>2.078860367666373</v>
+        <v>2.090027075743542</v>
       </c>
       <c r="E6" t="n">
-        <v>7.551796323713456</v>
+        <v>7.604803245520471</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469075142885929</v>
+        <v>0.7469306924155507</v>
       </c>
       <c r="G6" t="n">
-        <v>31.67633418182231</v>
+        <v>31.85320304835975</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35774565727527</v>
+        <v>34.35881185111533</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827398548759121</v>
+        <v>3.8328074793317</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668171964303705</v>
+        <v>4.668316827597192</v>
       </c>
       <c r="K6" t="n">
-        <v>15.09278544217116</v>
+        <v>14.84509977991646</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78902220649031</v>
+        <v>42.79572854422369</v>
       </c>
       <c r="M6" t="n">
-        <v>99.872611459951</v>
+        <v>99.87243114576522</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.49811935396248</v>
+        <v>83.92072614725539</v>
       </c>
       <c r="C7" t="n">
-        <v>41.17638631539647</v>
+        <v>41.59312436134057</v>
       </c>
       <c r="D7" t="n">
-        <v>2.010504654822651</v>
+        <v>2.030519376353666</v>
       </c>
       <c r="E7" t="n">
-        <v>7.835743997189081</v>
+        <v>7.921288237005852</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478597504139747</v>
+        <v>0.747879497271958</v>
       </c>
       <c r="G7" t="n">
-        <v>30.63477389381458</v>
+        <v>30.94627181593438</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40154851904283</v>
+        <v>34.40245687451007</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19356509859202</v>
+        <v>3.198063488229734</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674123440087341</v>
+        <v>4.674246857949739</v>
       </c>
       <c r="K7" t="n">
-        <v>16.50188064603752</v>
+        <v>16.0792738527446</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21541641221157</v>
+        <v>42.22113491148895</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89368337364556</v>
+        <v>99.89353312557412</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.3825217149632</v>
+        <v>88.86677910841414</v>
       </c>
       <c r="C8" t="n">
-        <v>43.51954789708491</v>
+        <v>43.91811311260287</v>
       </c>
       <c r="D8" t="n">
-        <v>2.014760359182035</v>
+        <v>2.034856641178322</v>
       </c>
       <c r="E8" t="n">
-        <v>9.694476946815636</v>
+        <v>9.772584700339678</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494427708722511</v>
+        <v>0.749476995662948</v>
       </c>
       <c r="G8" t="n">
-        <v>31.15298714421643</v>
+        <v>31.45500549665257</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47436746012354</v>
+        <v>34.47594180049561</v>
       </c>
       <c r="I8" t="n">
-        <v>5.61246971580174</v>
+        <v>5.694682251191577</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684017317951569</v>
+        <v>4.684231222893426</v>
       </c>
       <c r="K8" t="n">
-        <v>11.61747828503678</v>
+        <v>11.13322089158586</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67628666114449</v>
+        <v>44.75924785828381</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81331284326619</v>
+        <v>99.81058186247253</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.4082575100156</v>
+        <v>87.18891607717552</v>
       </c>
       <c r="C9" t="n">
-        <v>42.416912698889</v>
+        <v>43.12498889303816</v>
       </c>
       <c r="D9" t="n">
-        <v>1.925433038923275</v>
+        <v>1.959493145124457</v>
       </c>
       <c r="E9" t="n">
-        <v>10.04557691618007</v>
+        <v>10.20301030188244</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507973956652273</v>
+        <v>0.7508392326702304</v>
       </c>
       <c r="G9" t="n">
-        <v>29.77177431313899</v>
+        <v>30.29002948082447</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53668020060044</v>
+        <v>34.5386047028306</v>
       </c>
       <c r="I9" t="n">
-        <v>4.685511922599922</v>
+        <v>4.754194009654386</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69248372290767</v>
+        <v>4.692745204188941</v>
       </c>
       <c r="K9" t="n">
-        <v>13.59174248998438</v>
+        <v>12.81108392282449</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83544287457656</v>
+        <v>43.90574156604868</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84409806344995</v>
+        <v>99.84181438191133</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.29614916042027</v>
+        <v>85.31224148972507</v>
       </c>
       <c r="C10" t="n">
-        <v>41.03223885911775</v>
+        <v>41.98700229661425</v>
       </c>
       <c r="D10" t="n">
-        <v>1.830836465734698</v>
+        <v>1.87577461037371</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20380935139262</v>
+        <v>10.42841934506912</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519584181663572</v>
+        <v>0.7520033125977357</v>
       </c>
       <c r="G10" t="n">
-        <v>28.30908629915249</v>
+        <v>28.99590049037552</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59008723565242</v>
+        <v>34.59215237949584</v>
       </c>
       <c r="I10" t="n">
-        <v>3.910631276781949</v>
+        <v>3.967970648077279</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699740113539732</v>
+        <v>4.700020703735849</v>
       </c>
       <c r="K10" t="n">
-        <v>15.70385083957973</v>
+        <v>14.68775851027494</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13375719234138</v>
+        <v>43.1931782483982</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86984689103886</v>
+        <v>99.86793905528739</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.09415107071015</v>
+        <v>83.35917665969568</v>
       </c>
       <c r="C11" t="n">
-        <v>39.43683567762244</v>
+        <v>40.65013996284188</v>
       </c>
       <c r="D11" t="n">
-        <v>1.733201130587952</v>
+        <v>1.789436060794614</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20352076924996</v>
+        <v>10.50025455770181</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752954743161705</v>
+        <v>0.7529989630878774</v>
       </c>
       <c r="G11" t="n">
-        <v>26.79941179777274</v>
+        <v>27.66127106409277</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63591818543841</v>
+        <v>34.63795230204236</v>
       </c>
       <c r="I11" t="n">
-        <v>3.263177299738733</v>
+        <v>3.311020192677009</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705967144760655</v>
+        <v>4.706243519299234</v>
       </c>
       <c r="K11" t="n">
-        <v>17.90584892928985</v>
+        <v>16.64082334030432</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54868674651044</v>
+        <v>42.59881528996276</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89137135342273</v>
+        <v>99.88977859310897</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.76630221015118</v>
+        <v>81.30035346045673</v>
       </c>
       <c r="C12" t="n">
-        <v>37.61445864962157</v>
+        <v>39.10500136208771</v>
       </c>
       <c r="D12" t="n">
-        <v>1.630897666812128</v>
+        <v>1.699141886528252</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05498517528187</v>
+        <v>10.43080096310402</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538113496959238</v>
+        <v>0.7538517742109598</v>
       </c>
       <c r="G12" t="n">
-        <v>25.21755692491284</v>
+        <v>26.26549521905856</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67532208601248</v>
+        <v>34.67718161370415</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722408071836444</v>
+        <v>2.762308415032288</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711320935599523</v>
+        <v>4.711573588818499</v>
       </c>
       <c r="K12" t="n">
-        <v>20.23369778984879</v>
+        <v>18.69964653954327</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06119974664801</v>
+        <v>42.1033793152391</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90935618611837</v>
+        <v>99.90802721687008</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.42087238839515</v>
+        <v>79.12306169380395</v>
       </c>
       <c r="C13" t="n">
-        <v>35.68993352714621</v>
+        <v>37.35565202278126</v>
       </c>
       <c r="D13" t="n">
-        <v>1.528737790748495</v>
+        <v>1.604344411433142</v>
       </c>
       <c r="E13" t="n">
-        <v>9.803620075137133</v>
+        <v>10.23287851759468</v>
       </c>
       <c r="F13" t="n">
-        <v>0.75454837050148</v>
+        <v>0.754583543048215</v>
       </c>
       <c r="G13" t="n">
-        <v>23.6379222595985</v>
+        <v>24.80010692592615</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70922504306807</v>
+        <v>34.71084298021789</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270891533707222</v>
+        <v>2.304158171532517</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71592731563425</v>
+        <v>4.716147144051344</v>
       </c>
       <c r="K13" t="n">
-        <v>22.57912761160485</v>
+        <v>20.87693830619606</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65531641480904</v>
+        <v>41.69067888171622</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92437755356009</v>
+        <v>99.92326921069355</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.07823171702013</v>
+        <v>85.17240916835731</v>
       </c>
       <c r="C14" t="n">
-        <v>39.83796334004467</v>
+        <v>40.9947179201929</v>
       </c>
       <c r="D14" t="n">
-        <v>1.530499707809195</v>
+        <v>1.606296055359731</v>
       </c>
       <c r="E14" t="n">
-        <v>12.11611356002806</v>
+        <v>12.30794531451523</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554180105765508</v>
+        <v>0.7555014746210115</v>
       </c>
       <c r="G14" t="n">
-        <v>25.48184653283524</v>
+        <v>26.37484410112627</v>
       </c>
       <c r="H14" t="n">
-        <v>36.56590933138158</v>
+        <v>36.29763631224478</v>
       </c>
       <c r="I14" t="n">
-        <v>2.907082008286083</v>
+        <v>3.10830169410897</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721362566103442</v>
+        <v>4.721884216381323</v>
       </c>
       <c r="K14" t="n">
-        <v>15.92176828297984</v>
+        <v>14.82759083164268</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14347719815993</v>
+        <v>44.07420707753987</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90320882118444</v>
+        <v>99.89651582937545</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.40281874892948</v>
+        <v>84.5344400577066</v>
       </c>
       <c r="C15" t="n">
-        <v>39.6122262331981</v>
+        <v>40.83832640359778</v>
       </c>
       <c r="D15" t="n">
-        <v>1.505538794917026</v>
+        <v>1.582477007521313</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32266461691556</v>
+        <v>12.55758624005015</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561501302632798</v>
+        <v>0.7562739170243327</v>
       </c>
       <c r="G15" t="n">
-        <v>25.06626321165437</v>
+        <v>25.98374330044923</v>
       </c>
       <c r="H15" t="n">
-        <v>36.60134748841495</v>
+        <v>36.3347478657887</v>
       </c>
       <c r="I15" t="n">
-        <v>2.42491619261881</v>
+        <v>2.592899745470798</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725938314145499</v>
+        <v>4.72671198140208</v>
       </c>
       <c r="K15" t="n">
-        <v>16.59718125107052</v>
+        <v>15.46555994229339</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70984023772342</v>
+        <v>43.60977194038358</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91924772199204</v>
+        <v>99.91365828627474</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.02791214749418</v>
+        <v>82.31348131377428</v>
       </c>
       <c r="C16" t="n">
-        <v>37.61250406795644</v>
+        <v>39.0192466857614</v>
       </c>
       <c r="D16" t="n">
-        <v>1.41478630758873</v>
+        <v>1.496191903079924</v>
       </c>
       <c r="E16" t="n">
-        <v>11.91693990738892</v>
+        <v>12.2333198737166</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567792434612542</v>
+        <v>0.7569362426440801</v>
       </c>
       <c r="G16" t="n">
-        <v>23.55529202833871</v>
+        <v>24.56697073831941</v>
       </c>
       <c r="H16" t="n">
-        <v>36.63179962992366</v>
+        <v>36.36656892143645</v>
       </c>
       <c r="I16" t="n">
-        <v>2.022444759160069</v>
+        <v>2.162642118052303</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729870271632839</v>
+        <v>4.730851516525502</v>
       </c>
       <c r="K16" t="n">
-        <v>18.9720878525058</v>
+        <v>17.68651868622573</v>
       </c>
       <c r="L16" t="n">
-        <v>43.34804929640946</v>
+        <v>43.22220963508311</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93264121687172</v>
+        <v>99.92797500707024</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.67731701296813</v>
+        <v>83.80766204972973</v>
       </c>
       <c r="C17" t="n">
-        <v>38.82246296138054</v>
+        <v>40.11015551133735</v>
       </c>
       <c r="D17" t="n">
-        <v>1.415930354170684</v>
+        <v>1.497490774472116</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68352521771971</v>
+        <v>12.9546542917582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573912021027338</v>
+        <v>0.7575933527576024</v>
       </c>
       <c r="G17" t="n">
-        <v>23.99700941321649</v>
+        <v>24.9352374475611</v>
       </c>
       <c r="H17" t="n">
-        <v>37.08409114443872</v>
+        <v>36.74507907638044</v>
       </c>
       <c r="I17" t="n">
-        <v>2.005674668177714</v>
+        <v>2.182648652065256</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733695013142087</v>
+        <v>4.734958454735017</v>
       </c>
       <c r="K17" t="n">
-        <v>17.32268298703186</v>
+        <v>16.19233795027026</v>
       </c>
       <c r="L17" t="n">
-        <v>43.78805224763217</v>
+        <v>43.62481468844005</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93319819604457</v>
+        <v>99.92730815004766</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.43300249115175</v>
+        <v>81.64987877056566</v>
       </c>
       <c r="C18" t="n">
-        <v>36.88810759152902</v>
+        <v>38.29033823350513</v>
       </c>
       <c r="D18" t="n">
-        <v>1.333439600817608</v>
+        <v>1.416504639111831</v>
       </c>
       <c r="E18" t="n">
-        <v>12.22335413619503</v>
+        <v>12.55742163373673</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579161846779929</v>
+        <v>0.758156321843426</v>
       </c>
       <c r="G18" t="n">
-        <v>22.5989665088559</v>
+        <v>23.58670926321827</v>
       </c>
       <c r="H18" t="n">
-        <v>37.10979582864432</v>
+        <v>36.77238441571696</v>
       </c>
       <c r="I18" t="n">
-        <v>1.672554077723451</v>
+        <v>1.82022548541703</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736976154237456</v>
+        <v>4.738477011521414</v>
       </c>
       <c r="K18" t="n">
-        <v>19.56699750884825</v>
+        <v>18.35012122943433</v>
       </c>
       <c r="L18" t="n">
-        <v>43.48918171439558</v>
+        <v>43.29891140783651</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94428681477284</v>
+        <v>99.93937087077596</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.57230427883857</v>
+        <v>80.74183086647666</v>
       </c>
       <c r="C19" t="n">
-        <v>36.28527739569495</v>
+        <v>37.66355304901807</v>
       </c>
       <c r="D19" t="n">
-        <v>1.302457154698272</v>
+        <v>1.383126038089011</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17177960281497</v>
+        <v>12.51448529803668</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583589672916649</v>
+        <v>0.758631388888487</v>
       </c>
       <c r="G19" t="n">
-        <v>22.07387991191969</v>
+        <v>23.03091061900637</v>
       </c>
       <c r="H19" t="n">
-        <v>37.13147576202221</v>
+        <v>36.79542629705583</v>
       </c>
       <c r="I19" t="n">
-        <v>1.39460933451886</v>
+        <v>1.517805044847247</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739743545572905</v>
+        <v>4.741446180553045</v>
       </c>
       <c r="K19" t="n">
-        <v>20.42769572116142</v>
+        <v>19.25816913352332</v>
       </c>
       <c r="L19" t="n">
-        <v>43.24056704765132</v>
+        <v>43.02771599841923</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9535401645077</v>
+        <v>99.94943818096063</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.13185620066777</v>
+        <v>78.30104899408643</v>
       </c>
       <c r="C20" t="n">
-        <v>34.05972329945918</v>
+        <v>35.45717772785908</v>
       </c>
       <c r="D20" t="n">
-        <v>1.213650461891253</v>
+        <v>1.292404547759739</v>
       </c>
       <c r="E20" t="n">
-        <v>11.53565248331471</v>
+        <v>11.90455964396313</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587400412646937</v>
+        <v>0.7590400945257937</v>
       </c>
       <c r="G20" t="n">
-        <v>20.56879526070826</v>
+        <v>21.52027566784653</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1501342596511</v>
+        <v>36.815249492319</v>
       </c>
       <c r="I20" t="n">
-        <v>1.162758435933419</v>
+        <v>1.26551895688602</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742125257904335</v>
+        <v>4.744000590786212</v>
       </c>
       <c r="K20" t="n">
-        <v>22.86814379933223</v>
+        <v>21.69895100591357</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0333937530275</v>
+        <v>42.80171001498158</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96126085181891</v>
+        <v>99.95783874875424</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.76220873695438</v>
+        <v>83.59848106638586</v>
       </c>
       <c r="C21" t="n">
-        <v>37.54659698114705</v>
+        <v>38.62597325675879</v>
       </c>
       <c r="D21" t="n">
-        <v>1.214468340910646</v>
+        <v>1.29340255362835</v>
       </c>
       <c r="E21" t="n">
-        <v>13.4189084880066</v>
+        <v>13.65120386730982</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592513561617003</v>
+        <v>0.7596262317923026</v>
       </c>
       <c r="G21" t="n">
-        <v>22.17927144694227</v>
+        <v>22.95156791162939</v>
       </c>
       <c r="H21" t="n">
-        <v>38.77178460986931</v>
+        <v>38.25835264597797</v>
       </c>
       <c r="I21" t="n">
-        <v>1.673203519053227</v>
+        <v>1.93666390734614</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745320976010626</v>
+        <v>4.747663948701892</v>
       </c>
       <c r="K21" t="n">
-        <v>17.23779126304564</v>
+        <v>16.40151893361412</v>
       </c>
       <c r="L21" t="n">
-        <v>45.15987586558737</v>
+        <v>44.90800215786603</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94426410978008</v>
+        <v>99.93549434823895</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.55580739752585</v>
+        <v>45.69520388461939</v>
       </c>
       <c r="M2" t="n">
-        <v>99.41611275114525</v>
+        <v>98.69899760996239</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04449399340598</v>
+        <v>87.99424814590263</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91437771398322</v>
+        <v>45.93962765134413</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228785540114587</v>
+        <v>2.228637475002242</v>
       </c>
       <c r="E3" t="n">
-        <v>5.699200340445213</v>
+        <v>5.710683999302119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429285133715291</v>
+        <v>0.7428791583340809</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9679610778542</v>
+        <v>33.97728927212606</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17471161509033</v>
+        <v>34.17244128336772</v>
       </c>
       <c r="I3" t="n">
-        <v>6.587603697958063</v>
+        <v>6.519322218182411</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643303208572057</v>
+        <v>4.642994739588006</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95550600659401</v>
+        <v>12.00575185409737</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89366091557041</v>
+        <v>48.820600478605</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635446361477</v>
+        <v>106.7659799840465</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23409869200458</v>
+        <v>87.03801011435429</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74342512843387</v>
+        <v>42.60871329240814</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190268511661727</v>
+        <v>2.18233646084181</v>
       </c>
       <c r="E4" t="n">
-        <v>6.517577168229649</v>
+        <v>6.499391056343801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444902136182925</v>
+        <v>0.7444280238333285</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38093962613836</v>
+        <v>33.27139476511555</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24654982644145</v>
+        <v>34.24368909633311</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501209510800784</v>
+        <v>5.444095562928377</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653063835114328</v>
+        <v>4.652675148958304</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7659013079954</v>
+        <v>12.96198988564572</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30768457196077</v>
+        <v>44.24820453810773</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81701100839005</v>
+        <v>99.81890771616159</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.2406831205938</v>
+        <v>85.78883026276172</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60391682473734</v>
+        <v>42.20449483828198</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142368017054823</v>
+        <v>2.121095034701881</v>
       </c>
       <c r="E5" t="n">
-        <v>7.140452897728013</v>
+        <v>7.074462659767985</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458117304723393</v>
+        <v>0.7457425869349534</v>
       </c>
       <c r="G5" t="n">
-        <v>32.65090880570615</v>
+        <v>32.33772220745033</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30733960172761</v>
+        <v>34.30415899900785</v>
       </c>
       <c r="I5" t="n">
-        <v>4.592478752452753</v>
+        <v>4.544757606555265</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661323315452121</v>
+        <v>4.66089116834346</v>
       </c>
       <c r="K5" t="n">
-        <v>13.75931687940621</v>
+        <v>14.21116973723828</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48395492055644</v>
+        <v>43.43311054773172</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84718862469998</v>
+        <v>99.84877512325198</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.15490022008355</v>
+        <v>84.32543532485867</v>
       </c>
       <c r="C6" t="n">
-        <v>42.23160282162507</v>
+        <v>41.4468438851959</v>
       </c>
       <c r="D6" t="n">
-        <v>2.090027075743542</v>
+        <v>2.049427982723162</v>
       </c>
       <c r="E6" t="n">
-        <v>7.604803245520471</v>
+        <v>7.46759514910904</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469306924155507</v>
+        <v>0.7468607090701164</v>
       </c>
       <c r="G6" t="n">
-        <v>31.85320304835975</v>
+        <v>31.24510297992925</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35881185111533</v>
+        <v>34.35559261722535</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8328074793317</v>
+        <v>3.79297645511352</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668316827597192</v>
+        <v>4.667879431688228</v>
       </c>
       <c r="K6" t="n">
-        <v>14.84509977991646</v>
+        <v>15.67456467514132</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79572854422369</v>
+        <v>42.75234817281404</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87243114576522</v>
+        <v>99.87375673315125</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.92072614725539</v>
+        <v>82.63625286991554</v>
       </c>
       <c r="C7" t="n">
-        <v>41.59312436134057</v>
+        <v>40.34660665132085</v>
       </c>
       <c r="D7" t="n">
-        <v>2.030519376353666</v>
+        <v>1.967007606170463</v>
       </c>
       <c r="E7" t="n">
-        <v>7.921288237005852</v>
+        <v>7.694751037237809</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747879497271958</v>
+        <v>0.7478141652049897</v>
       </c>
       <c r="G7" t="n">
-        <v>30.94627181593438</v>
+        <v>29.98854106375409</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40245687451007</v>
+        <v>34.39945159942952</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198063488229734</v>
+        <v>3.164848865587475</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674246857949739</v>
+        <v>4.673838532531186</v>
       </c>
       <c r="K7" t="n">
-        <v>16.0792738527446</v>
+        <v>17.36374713008448</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22113491148895</v>
+        <v>42.18428576150818</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89353312557412</v>
+        <v>99.8946395429135</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.86677910841414</v>
+        <v>87.6648721857637</v>
       </c>
       <c r="C8" t="n">
-        <v>43.91811311260287</v>
+        <v>42.73449539553431</v>
       </c>
       <c r="D8" t="n">
-        <v>2.034856641178322</v>
+        <v>1.97125612362985</v>
       </c>
       <c r="E8" t="n">
-        <v>9.772584700339678</v>
+        <v>9.587900015915768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749476995662948</v>
+        <v>0.7494293605541507</v>
       </c>
       <c r="G8" t="n">
-        <v>31.45500549665257</v>
+        <v>30.51821164822721</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47594180049561</v>
+        <v>34.47375058549093</v>
       </c>
       <c r="I8" t="n">
-        <v>5.694682251191577</v>
+        <v>5.680390948482347</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684231222893426</v>
+        <v>4.683933503463443</v>
       </c>
       <c r="K8" t="n">
-        <v>11.13322089158586</v>
+        <v>12.3351278142363</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75924785828381</v>
+        <v>44.7414385109304</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81058186247253</v>
+        <v>99.81106172070102</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.18891607717552</v>
+        <v>85.49473536404764</v>
       </c>
       <c r="C9" t="n">
-        <v>43.12498889303816</v>
+        <v>41.44560351390015</v>
       </c>
       <c r="D9" t="n">
-        <v>1.959493145124457</v>
+        <v>1.873045632611466</v>
       </c>
       <c r="E9" t="n">
-        <v>10.20301030188244</v>
+        <v>9.900620573285748</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508392326702304</v>
+        <v>0.7508150609126554</v>
       </c>
       <c r="G9" t="n">
-        <v>30.29002948082447</v>
+        <v>28.99775547054071</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5386047028306</v>
+        <v>34.53749280198215</v>
       </c>
       <c r="I9" t="n">
-        <v>4.754194009654386</v>
+        <v>4.742411694010824</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692745204188941</v>
+        <v>4.692594130704098</v>
       </c>
       <c r="K9" t="n">
-        <v>12.81108392282449</v>
+        <v>14.50526463595235</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90574156604868</v>
+        <v>43.89134321268966</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84181438191133</v>
+        <v>99.84221136254216</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.31224148972507</v>
+        <v>83.02143752212461</v>
       </c>
       <c r="C10" t="n">
-        <v>41.98700229661425</v>
+        <v>39.70760718626236</v>
       </c>
       <c r="D10" t="n">
-        <v>1.87577461037371</v>
+        <v>1.762218120887171</v>
       </c>
       <c r="E10" t="n">
-        <v>10.42841934506912</v>
+        <v>9.974519105708088</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520033125977357</v>
+        <v>0.7520083045843088</v>
       </c>
       <c r="G10" t="n">
-        <v>28.99590049037552</v>
+        <v>27.28196754288147</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59215237949584</v>
+        <v>34.5923820108782</v>
       </c>
       <c r="I10" t="n">
-        <v>3.967970648077279</v>
+        <v>3.958290533533444</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700020703735849</v>
+        <v>4.700051903651932</v>
       </c>
       <c r="K10" t="n">
-        <v>14.68775851027494</v>
+        <v>16.97856247787539</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1931782483982</v>
+        <v>43.18209667769527</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86793905528739</v>
+        <v>99.86826634183302</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.35917665969568</v>
+        <v>80.4775830749592</v>
       </c>
       <c r="C11" t="n">
-        <v>40.65013996284188</v>
+        <v>37.77662120099748</v>
       </c>
       <c r="D11" t="n">
-        <v>1.789436060794614</v>
+        <v>1.649582698767165</v>
       </c>
       <c r="E11" t="n">
-        <v>10.50025455770181</v>
+        <v>9.887494031114308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529989630878774</v>
+        <v>0.7530371417377567</v>
       </c>
       <c r="G11" t="n">
-        <v>27.66127106409277</v>
+        <v>25.53819025785974</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63795230204236</v>
+        <v>34.63970851993681</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311020192677009</v>
+        <v>3.303088289682433</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706243519299234</v>
+        <v>4.706482135860981</v>
       </c>
       <c r="K11" t="n">
-        <v>16.64082334030432</v>
+        <v>19.52241692504082</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59881528996276</v>
+        <v>42.59100935914134</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88977859310897</v>
+        <v>99.89004748517964</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>81.30035346045673</v>
+        <v>77.89633151638469</v>
       </c>
       <c r="C12" t="n">
-        <v>39.10500136208771</v>
+        <v>35.70581483336039</v>
       </c>
       <c r="D12" t="n">
-        <v>1.699141886528252</v>
+        <v>1.536545435928677</v>
       </c>
       <c r="E12" t="n">
-        <v>10.43080096310402</v>
+        <v>9.669259115949252</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538517742109598</v>
+        <v>0.7539251743626056</v>
       </c>
       <c r="G12" t="n">
-        <v>26.26549521905856</v>
+        <v>23.78819183295235</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67718161370415</v>
+        <v>34.68055802067986</v>
       </c>
       <c r="I12" t="n">
-        <v>2.762308415032288</v>
+        <v>2.755819596745671</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711573588818499</v>
+        <v>4.712032339766287</v>
       </c>
       <c r="K12" t="n">
-        <v>18.69964653954327</v>
+        <v>22.10366848361529</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1033793152391</v>
+        <v>42.09876423053315</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90802721687008</v>
+        <v>99.90824754750884</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79.12306169380395</v>
+        <v>75.20967013519406</v>
       </c>
       <c r="C13" t="n">
-        <v>37.35565202278126</v>
+        <v>33.44401289977247</v>
       </c>
       <c r="D13" t="n">
-        <v>1.604344411433142</v>
+        <v>1.420022617719904</v>
       </c>
       <c r="E13" t="n">
-        <v>10.23287851759468</v>
+        <v>9.319140499342398</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754583543048215</v>
+        <v>0.7546933227213317</v>
       </c>
       <c r="G13" t="n">
-        <v>24.80010692592615</v>
+        <v>21.98423141131262</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71084298021789</v>
+        <v>34.71589284518126</v>
       </c>
       <c r="I13" t="n">
-        <v>2.304158171532517</v>
+        <v>2.298856171908223</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716147144051344</v>
+        <v>4.716833267008325</v>
       </c>
       <c r="K13" t="n">
-        <v>20.87693830619606</v>
+        <v>24.79032986480594</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69067888171622</v>
+        <v>41.68910669106754</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92326921069355</v>
+        <v>99.92344945564595</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85.17240916835731</v>
+        <v>82.67698321874867</v>
       </c>
       <c r="C14" t="n">
-        <v>40.9947179201929</v>
+        <v>38.04428343858571</v>
       </c>
       <c r="D14" t="n">
-        <v>1.606296055359731</v>
+        <v>1.421782654236691</v>
       </c>
       <c r="E14" t="n">
-        <v>12.30794531451523</v>
+        <v>11.87280203776622</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555014746210115</v>
+        <v>0.7556287217708888</v>
       </c>
       <c r="G14" t="n">
-        <v>26.37484410112627</v>
+        <v>24.04122373016234</v>
       </c>
       <c r="H14" t="n">
-        <v>36.29763631224478</v>
+        <v>36.78866532750398</v>
       </c>
       <c r="I14" t="n">
-        <v>3.10830169410897</v>
+        <v>3.074201236240505</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721884216381323</v>
+        <v>4.722679511068057</v>
       </c>
       <c r="K14" t="n">
-        <v>14.82759083164268</v>
+        <v>17.32301678125131</v>
       </c>
       <c r="L14" t="n">
-        <v>44.07420707753987</v>
+        <v>44.53035325826023</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89651582937545</v>
+        <v>99.89765347809725</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.5344400577066</v>
+        <v>81.74947707516152</v>
       </c>
       <c r="C15" t="n">
-        <v>40.83832640359778</v>
+        <v>37.56177493988625</v>
       </c>
       <c r="D15" t="n">
-        <v>1.582477007521313</v>
+        <v>1.384580948271273</v>
       </c>
       <c r="E15" t="n">
-        <v>12.55758624005015</v>
+        <v>12.0187215861672</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562739170243327</v>
+        <v>0.7564188674358945</v>
       </c>
       <c r="G15" t="n">
-        <v>25.98374330044923</v>
+        <v>23.44133112604362</v>
       </c>
       <c r="H15" t="n">
-        <v>36.3347478657887</v>
+        <v>36.85629340387749</v>
       </c>
       <c r="I15" t="n">
-        <v>2.592899745470798</v>
+        <v>2.564513221891685</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72671198140208</v>
+        <v>4.727617921474342</v>
       </c>
       <c r="K15" t="n">
-        <v>15.46555994229339</v>
+        <v>18.25052292483849</v>
       </c>
       <c r="L15" t="n">
-        <v>43.60977194038358</v>
+        <v>44.1023076564908</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91365828627474</v>
+        <v>99.91460552121555</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.31348131377428</v>
+        <v>79.04050136492512</v>
       </c>
       <c r="C16" t="n">
-        <v>39.0192466857614</v>
+        <v>35.248259209611</v>
       </c>
       <c r="D16" t="n">
-        <v>1.496191903079924</v>
+        <v>1.283937779183734</v>
       </c>
       <c r="E16" t="n">
-        <v>12.2333198737166</v>
+        <v>11.5016019452693</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569362426440801</v>
+        <v>0.7571012166559131</v>
       </c>
       <c r="G16" t="n">
-        <v>24.56697073831941</v>
+        <v>21.73741496635575</v>
       </c>
       <c r="H16" t="n">
-        <v>36.36656892143645</v>
+        <v>36.88954067485337</v>
       </c>
       <c r="I16" t="n">
-        <v>2.162642118052303</v>
+        <v>2.139022178507596</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730851516525502</v>
+        <v>4.731882604099458</v>
       </c>
       <c r="K16" t="n">
-        <v>17.68651868622573</v>
+        <v>20.95949863507488</v>
       </c>
       <c r="L16" t="n">
-        <v>43.22220963508311</v>
+        <v>43.72100567692823</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92797500707024</v>
+        <v>99.92876352161412</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.80766204972973</v>
+        <v>80.98744450712512</v>
       </c>
       <c r="C17" t="n">
-        <v>40.11015551133735</v>
+        <v>36.6359444029148</v>
       </c>
       <c r="D17" t="n">
-        <v>1.497490774472116</v>
+        <v>1.285080323708535</v>
       </c>
       <c r="E17" t="n">
-        <v>12.9546542917582</v>
+        <v>12.37055628790827</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575933527576024</v>
+        <v>0.7577749423331497</v>
       </c>
       <c r="G17" t="n">
-        <v>24.9352374475611</v>
+        <v>22.25513427121995</v>
       </c>
       <c r="H17" t="n">
-        <v>36.74507907638044</v>
+        <v>37.4207434822268</v>
       </c>
       <c r="I17" t="n">
-        <v>2.182648652065256</v>
+        <v>2.162061810146221</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734958454735017</v>
+        <v>4.736093389582186</v>
       </c>
       <c r="K17" t="n">
-        <v>16.19233795027026</v>
+        <v>19.01255549287486</v>
       </c>
       <c r="L17" t="n">
-        <v>43.62481468844005</v>
+        <v>44.27949545236709</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92730815004766</v>
+        <v>99.92799534815677</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.64987877056566</v>
+        <v>78.37026220723583</v>
       </c>
       <c r="C18" t="n">
-        <v>38.29033823350513</v>
+        <v>34.3516498878009</v>
       </c>
       <c r="D18" t="n">
-        <v>1.416504639111831</v>
+        <v>1.192337199975272</v>
       </c>
       <c r="E18" t="n">
-        <v>12.55742163373673</v>
+        <v>11.77830070977878</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758156321843426</v>
+        <v>0.7583560913193693</v>
       </c>
       <c r="G18" t="n">
-        <v>23.58670926321827</v>
+        <v>20.64900068304101</v>
       </c>
       <c r="H18" t="n">
-        <v>36.77238441571696</v>
+        <v>37.44944201252041</v>
       </c>
       <c r="I18" t="n">
-        <v>1.82022548541703</v>
+        <v>1.803099939854928</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738477011521414</v>
+        <v>4.739725570746059</v>
       </c>
       <c r="K18" t="n">
-        <v>18.35012122943433</v>
+        <v>21.62973779276417</v>
       </c>
       <c r="L18" t="n">
-        <v>43.29891140783651</v>
+        <v>43.95855504693084</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93937087077596</v>
+        <v>99.93994272749592</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.74183086647666</v>
+        <v>77.34802722766587</v>
       </c>
       <c r="C19" t="n">
-        <v>37.66355304901807</v>
+        <v>33.59786312226068</v>
       </c>
       <c r="D19" t="n">
-        <v>1.383126038089011</v>
+        <v>1.156493063481887</v>
       </c>
       <c r="E19" t="n">
-        <v>12.51448529803668</v>
+        <v>11.67615813738693</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758631388888487</v>
+        <v>0.758850114132062</v>
       </c>
       <c r="G19" t="n">
-        <v>23.03091061900637</v>
+        <v>20.02824876911073</v>
       </c>
       <c r="H19" t="n">
-        <v>36.79542629705583</v>
+        <v>37.47383804347285</v>
       </c>
       <c r="I19" t="n">
-        <v>1.517805044847247</v>
+        <v>1.511625886756036</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741446180553045</v>
+        <v>4.742813213325388</v>
       </c>
       <c r="K19" t="n">
-        <v>19.25816913352332</v>
+        <v>22.65197277233413</v>
       </c>
       <c r="L19" t="n">
-        <v>43.02771599841923</v>
+        <v>43.6998093788846</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94943818096063</v>
+        <v>99.9496452734794</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.30104899408643</v>
+        <v>74.65344393877373</v>
       </c>
       <c r="C20" t="n">
-        <v>35.45717772785908</v>
+        <v>31.1351148350467</v>
       </c>
       <c r="D20" t="n">
-        <v>1.292404547759739</v>
+        <v>1.062258480472026</v>
       </c>
       <c r="E20" t="n">
-        <v>11.90455964396313</v>
+        <v>10.93481534479755</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590400945257937</v>
+        <v>0.7592771774976367</v>
       </c>
       <c r="G20" t="n">
-        <v>21.52027566784653</v>
+        <v>18.39628595777091</v>
       </c>
       <c r="H20" t="n">
-        <v>36.815249492319</v>
+        <v>37.49492745638563</v>
       </c>
       <c r="I20" t="n">
-        <v>1.26551895688602</v>
+        <v>1.260397162489746</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744000590786212</v>
+        <v>4.74548235936023</v>
       </c>
       <c r="K20" t="n">
-        <v>21.69895100591357</v>
+        <v>25.34655606122626</v>
       </c>
       <c r="L20" t="n">
-        <v>42.80171001498158</v>
+        <v>43.4763394957616</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95783874875424</v>
+        <v>99.95801039203457</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.59848106638586</v>
+        <v>81.3122557350752</v>
       </c>
       <c r="C21" t="n">
-        <v>38.62597325675879</v>
+        <v>35.29234687153262</v>
       </c>
       <c r="D21" t="n">
-        <v>1.29340255362835</v>
+        <v>1.063042732342763</v>
       </c>
       <c r="E21" t="n">
-        <v>13.65120386730982</v>
+        <v>13.16435098236493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596262317923026</v>
+        <v>0.7598377421415602</v>
       </c>
       <c r="G21" t="n">
-        <v>22.95156791162939</v>
+        <v>20.33117130368356</v>
       </c>
       <c r="H21" t="n">
-        <v>38.25835264597797</v>
+        <v>39.44391308542068</v>
       </c>
       <c r="I21" t="n">
-        <v>1.93666390734614</v>
+        <v>1.800954000736931</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747663948701892</v>
+        <v>4.748985888384753</v>
       </c>
       <c r="K21" t="n">
-        <v>16.40151893361412</v>
+        <v>18.6877442649248</v>
       </c>
       <c r="L21" t="n">
-        <v>44.90800215786603</v>
+        <v>45.95992135153207</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93549434823895</v>
+        <v>99.94001248798949</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_24_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.69520388461939</v>
+        <v>43.54698971620583</v>
       </c>
       <c r="M2" t="n">
-        <v>98.69899760996239</v>
+        <v>96.5354831675366</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99424814590263</v>
+        <v>81.48821006233284</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93962765134413</v>
+        <v>43.24376561788841</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228637475002242</v>
+        <v>2.180112954656939</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710683999302119</v>
+        <v>4.162679668667482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428791583340809</v>
+        <v>0.7376409592924874</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97728927212606</v>
+        <v>32.79253235963145</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17244128336772</v>
+        <v>33.93148412745442</v>
       </c>
       <c r="I3" t="n">
-        <v>6.519322218182411</v>
+        <v>3.073503997052031</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642994739588006</v>
+        <v>4.610255995578046</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00575185409737</v>
+        <v>18.51178993766715</v>
       </c>
       <c r="L3" t="n">
-        <v>48.820600478605</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7659799840465</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03801011435429</v>
+        <v>88.55813176697191</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60871329240814</v>
+        <v>42.79555074309131</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18233646084181</v>
+        <v>2.185862327078473</v>
       </c>
       <c r="E4" t="n">
-        <v>6.499391056343801</v>
+        <v>6.516426643765544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444280238333285</v>
+        <v>0.7395862587685035</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27139476511555</v>
+        <v>33.4665355185905</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24368909633311</v>
+        <v>34.02096790335116</v>
       </c>
       <c r="I4" t="n">
-        <v>5.444095562928377</v>
+        <v>7.006338998114593</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652675148958304</v>
+        <v>4.622414117303147</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96198988564572</v>
+        <v>11.44186823302808</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24820453810773</v>
+        <v>45.52965067224034</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81890771616159</v>
+        <v>99.76706964835972</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.78883026276172</v>
+        <v>87.50920574376831</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20449483828198</v>
+        <v>42.83258736362642</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121095034701881</v>
+        <v>2.136241220907932</v>
       </c>
       <c r="E5" t="n">
-        <v>7.074462659767985</v>
+        <v>7.343769346530618</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457425869349534</v>
+        <v>0.7412347653453124</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33772220745033</v>
+        <v>32.70681406149961</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30415899900785</v>
+        <v>34.09679920588437</v>
       </c>
       <c r="I5" t="n">
-        <v>4.544757606555265</v>
+        <v>5.851629860192256</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66089116834346</v>
+        <v>4.632717283408202</v>
       </c>
       <c r="K5" t="n">
-        <v>14.21116973723828</v>
+        <v>12.49079425623171</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43311054773172</v>
+        <v>44.48199785241646</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84877512325198</v>
+        <v>99.80537947227458</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.32543532485867</v>
+        <v>86.23201496081654</v>
       </c>
       <c r="C6" t="n">
-        <v>41.4468438851959</v>
+        <v>42.46359498080287</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049427982723162</v>
+        <v>2.075479523332065</v>
       </c>
       <c r="E6" t="n">
-        <v>7.46759514910904</v>
+        <v>7.949149724122576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468607090701164</v>
+        <v>0.7426346137281505</v>
       </c>
       <c r="G6" t="n">
-        <v>31.24510297992925</v>
+        <v>31.77652513849571</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35559261722535</v>
+        <v>34.16119223149492</v>
       </c>
       <c r="I6" t="n">
-        <v>3.79297645511352</v>
+        <v>4.885567393842186</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667879431688228</v>
+        <v>4.64146633580094</v>
       </c>
       <c r="K6" t="n">
-        <v>15.67456467514132</v>
+        <v>13.76798503918345</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75234817281404</v>
+        <v>43.60587470611945</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87375673315125</v>
+        <v>99.83745472610578</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.63625286991554</v>
+        <v>84.73452107923129</v>
       </c>
       <c r="C7" t="n">
-        <v>40.34660665132085</v>
+        <v>41.72484614501575</v>
       </c>
       <c r="D7" t="n">
-        <v>1.967007606170463</v>
+        <v>2.00433721400259</v>
       </c>
       <c r="E7" t="n">
-        <v>7.694751037237809</v>
+        <v>8.356312047529959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478141652049897</v>
+        <v>0.7438259200232826</v>
       </c>
       <c r="G7" t="n">
-        <v>29.98854106375409</v>
+        <v>30.68730437991682</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39945159942952</v>
+        <v>34.215992321071</v>
       </c>
       <c r="I7" t="n">
-        <v>3.164848865587475</v>
+        <v>4.077837196542125</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673838532531186</v>
+        <v>4.648912000145516</v>
       </c>
       <c r="K7" t="n">
-        <v>17.36374713008448</v>
+        <v>15.26547892076872</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18428576150818</v>
+        <v>42.87396472883102</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8946395429135</v>
+        <v>99.86428979461547</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.6648721857637</v>
+        <v>82.91062466772006</v>
       </c>
       <c r="C8" t="n">
-        <v>42.73449539553431</v>
+        <v>40.53424942725894</v>
       </c>
       <c r="D8" t="n">
-        <v>1.97125612362985</v>
+        <v>1.917898129064836</v>
       </c>
       <c r="E8" t="n">
-        <v>9.587900015915768</v>
+        <v>8.563078685395281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494293605541507</v>
+        <v>0.7448435320847685</v>
       </c>
       <c r="G8" t="n">
-        <v>30.51821164822721</v>
+        <v>29.36388310565468</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47375058549093</v>
+        <v>34.26280247589935</v>
       </c>
       <c r="I8" t="n">
-        <v>5.680390948482347</v>
+        <v>3.402846664091349</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683933503463443</v>
+        <v>4.655272075529802</v>
       </c>
       <c r="K8" t="n">
-        <v>12.3351278142363</v>
+        <v>17.08937533227994</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7414385109304</v>
+        <v>42.26310198500162</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81106172070102</v>
+        <v>99.8867267445405</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.49473536404764</v>
+        <v>80.96863758083326</v>
       </c>
       <c r="C9" t="n">
-        <v>41.44560351390015</v>
+        <v>39.12033395754768</v>
       </c>
       <c r="D9" t="n">
-        <v>1.873045632611466</v>
+        <v>1.826554583967241</v>
       </c>
       <c r="E9" t="n">
-        <v>9.900620573285748</v>
+        <v>8.628415756259013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508150609126554</v>
+        <v>0.7457140854399598</v>
       </c>
       <c r="G9" t="n">
-        <v>28.99775547054071</v>
+        <v>27.96537234011694</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53749280198215</v>
+        <v>34.30284793023814</v>
       </c>
       <c r="I9" t="n">
-        <v>4.742411694010824</v>
+        <v>2.839019850812223</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692594130704098</v>
+        <v>4.660713033999747</v>
       </c>
       <c r="K9" t="n">
-        <v>14.50526463595235</v>
+        <v>19.03136241916674</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89134321268966</v>
+        <v>41.7537801048386</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84221136254216</v>
+        <v>99.90547648155302</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.02143752212461</v>
+        <v>85.63637331590732</v>
       </c>
       <c r="C10" t="n">
-        <v>39.70760718626236</v>
+        <v>42.40371801849886</v>
       </c>
       <c r="D10" t="n">
-        <v>1.762218120887171</v>
+        <v>1.828540178050317</v>
       </c>
       <c r="E10" t="n">
-        <v>9.974519105708088</v>
+        <v>10.49111785849576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520083045843088</v>
+        <v>0.7465247294189092</v>
       </c>
       <c r="G10" t="n">
-        <v>27.28196754288147</v>
+        <v>29.38363109458369</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5923820108782</v>
+        <v>35.72799596912258</v>
       </c>
       <c r="I10" t="n">
-        <v>3.958290533533444</v>
+        <v>2.792783927367878</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700051903651932</v>
+        <v>4.665779558868182</v>
       </c>
       <c r="K10" t="n">
-        <v>16.97856247787539</v>
+        <v>14.36362668409268</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18209667769527</v>
+        <v>43.1396635883975</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86826634183302</v>
+        <v>99.90700829098904</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.4775830749592</v>
+        <v>85.13488677110101</v>
       </c>
       <c r="C11" t="n">
-        <v>37.77662120099748</v>
+        <v>42.20772146925094</v>
       </c>
       <c r="D11" t="n">
-        <v>1.649582698767165</v>
+        <v>1.797539133539223</v>
       </c>
       <c r="E11" t="n">
-        <v>9.887494031114308</v>
+        <v>10.76556890644219</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530371417377567</v>
+        <v>0.7472273936249787</v>
       </c>
       <c r="G11" t="n">
-        <v>25.53819025785974</v>
+        <v>28.93711392934645</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63970851993681</v>
+        <v>35.8132773441307</v>
       </c>
       <c r="I11" t="n">
-        <v>3.303088289682433</v>
+        <v>2.403988853861359</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706482135860981</v>
+        <v>4.670171210156115</v>
       </c>
       <c r="K11" t="n">
-        <v>19.52241692504082</v>
+        <v>14.86511322889899</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59100935914134</v>
+        <v>42.84710769404259</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89004748517964</v>
+        <v>99.91994239219252</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.89633151638469</v>
+        <v>82.96174895784253</v>
       </c>
       <c r="C12" t="n">
-        <v>35.70581483336039</v>
+        <v>40.40819889050843</v>
       </c>
       <c r="D12" t="n">
-        <v>1.536545435928677</v>
+        <v>1.70478413257056</v>
       </c>
       <c r="E12" t="n">
-        <v>9.669259115949252</v>
+        <v>10.54420999197862</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539251743626056</v>
+        <v>0.7478293354869695</v>
       </c>
       <c r="G12" t="n">
-        <v>23.78819183295235</v>
+        <v>27.44392694917644</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68055802067986</v>
+        <v>35.84212734485664</v>
       </c>
       <c r="I12" t="n">
-        <v>2.755819596745671</v>
+        <v>2.004937856979735</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712032339766287</v>
+        <v>4.673933346793558</v>
       </c>
       <c r="K12" t="n">
-        <v>22.10366848361529</v>
+        <v>17.03825104215748</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09876423053315</v>
+        <v>42.48677259917127</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90824754750884</v>
+        <v>99.93322253183719</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.20967013519406</v>
+        <v>83.9450183710309</v>
       </c>
       <c r="C13" t="n">
-        <v>33.44401289977247</v>
+        <v>41.27094775630793</v>
       </c>
       <c r="D13" t="n">
-        <v>1.420022617719904</v>
+        <v>1.70602699019872</v>
       </c>
       <c r="E13" t="n">
-        <v>9.319140499342398</v>
+        <v>11.1202968640917</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546933227213317</v>
+        <v>0.7483745337771306</v>
       </c>
       <c r="G13" t="n">
-        <v>21.98423141131262</v>
+        <v>27.72633758366912</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71589284518126</v>
+        <v>36.13066061225349</v>
       </c>
       <c r="I13" t="n">
-        <v>2.298856171908223</v>
+        <v>1.835980950933672</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716833267008325</v>
+        <v>4.677340836107065</v>
       </c>
       <c r="K13" t="n">
-        <v>24.79032986480594</v>
+        <v>16.05498162896908</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68910669106754</v>
+        <v>42.61291583403791</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92344945564595</v>
+        <v>99.93884521931493</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.67698321874867</v>
+        <v>81.66448717640485</v>
       </c>
       <c r="C14" t="n">
-        <v>38.04428343858571</v>
+        <v>39.27550213140697</v>
       </c>
       <c r="D14" t="n">
-        <v>1.421782654236691</v>
+        <v>1.611092490304756</v>
       </c>
       <c r="E14" t="n">
-        <v>11.87280203776622</v>
+        <v>10.75664751464141</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556287217708888</v>
+        <v>0.74884218570943</v>
       </c>
       <c r="G14" t="n">
-        <v>24.04122373016234</v>
+        <v>26.18346281819414</v>
       </c>
       <c r="H14" t="n">
-        <v>36.78866532750398</v>
+        <v>36.15323830896544</v>
       </c>
       <c r="I14" t="n">
-        <v>3.074201236240505</v>
+        <v>1.530940197905737</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722679511068057</v>
+        <v>4.680263660683937</v>
       </c>
       <c r="K14" t="n">
-        <v>17.32301678125131</v>
+        <v>18.33551282359513</v>
       </c>
       <c r="L14" t="n">
-        <v>44.53035325826023</v>
+        <v>42.33798557413861</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89765347809725</v>
+        <v>99.9490005291407</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.74947707516152</v>
+        <v>80.54461738764758</v>
       </c>
       <c r="C15" t="n">
-        <v>37.56177493988625</v>
+        <v>38.3569780114992</v>
       </c>
       <c r="D15" t="n">
-        <v>1.384580948271273</v>
+        <v>1.563401142061285</v>
       </c>
       <c r="E15" t="n">
-        <v>12.0187215861672</v>
+        <v>10.65675842157214</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564188674358945</v>
+        <v>0.7492485264951229</v>
       </c>
       <c r="G15" t="n">
-        <v>23.44133112604362</v>
+        <v>25.40838339165776</v>
       </c>
       <c r="H15" t="n">
-        <v>36.85629340387749</v>
+        <v>36.17285597412928</v>
       </c>
       <c r="I15" t="n">
-        <v>2.564513221891685</v>
+        <v>1.311166641137456</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727617921474342</v>
+        <v>4.682803290594518</v>
       </c>
       <c r="K15" t="n">
-        <v>18.25052292483849</v>
+        <v>19.45538261235243</v>
       </c>
       <c r="L15" t="n">
-        <v>44.1023076564908</v>
+        <v>42.14395752432581</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91460552121555</v>
+        <v>99.95631814817743</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.04050136492512</v>
+        <v>77.94531271345258</v>
       </c>
       <c r="C16" t="n">
-        <v>35.248259209611</v>
+        <v>35.96059328552709</v>
       </c>
       <c r="D16" t="n">
-        <v>1.283937779183734</v>
+        <v>1.456084891179363</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5016019452693</v>
+        <v>10.10744016541791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571012166559131</v>
+        <v>0.7495987894953413</v>
       </c>
       <c r="G16" t="n">
-        <v>21.73741496635575</v>
+        <v>23.66428050391897</v>
       </c>
       <c r="H16" t="n">
-        <v>36.88954067485337</v>
+        <v>36.18976626839337</v>
       </c>
       <c r="I16" t="n">
-        <v>2.139022178507596</v>
+        <v>1.093149660701743</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731882604099458</v>
+        <v>4.684992434345883</v>
       </c>
       <c r="K16" t="n">
-        <v>20.95949863507488</v>
+        <v>22.05468728654741</v>
       </c>
       <c r="L16" t="n">
-        <v>43.72100567692823</v>
+        <v>41.94829813233835</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92876352161412</v>
+        <v>99.96357870441285</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.98744450712512</v>
+        <v>83.08832568935104</v>
       </c>
       <c r="C17" t="n">
-        <v>36.6359444029148</v>
+        <v>39.40738499644163</v>
       </c>
       <c r="D17" t="n">
-        <v>1.285080323708535</v>
+        <v>1.456756170145793</v>
       </c>
       <c r="E17" t="n">
-        <v>12.37055628790827</v>
+        <v>11.92364351768763</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577749423331497</v>
+        <v>0.7499443668059075</v>
       </c>
       <c r="G17" t="n">
-        <v>22.25513427121995</v>
+        <v>25.29520839126241</v>
       </c>
       <c r="H17" t="n">
-        <v>37.4207434822268</v>
+        <v>37.82646860967761</v>
       </c>
       <c r="I17" t="n">
-        <v>2.162061810146221</v>
+        <v>1.149152341234772</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736093389582186</v>
+        <v>4.687152292536922</v>
       </c>
       <c r="K17" t="n">
-        <v>19.01255549287486</v>
+        <v>16.91167431064894</v>
       </c>
       <c r="L17" t="n">
-        <v>44.27949545236709</v>
+        <v>43.64265326599872</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92799534815677</v>
+        <v>99.9617125730893</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.37026220723583</v>
+        <v>84.68938929786789</v>
       </c>
       <c r="C18" t="n">
-        <v>34.3516498878009</v>
+        <v>40.14780002406687</v>
       </c>
       <c r="D18" t="n">
-        <v>1.192337199975272</v>
+        <v>1.457882311609456</v>
       </c>
       <c r="E18" t="n">
-        <v>11.77830070977878</v>
+        <v>12.52384650831569</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583560913193693</v>
+        <v>0.7505241092941898</v>
       </c>
       <c r="G18" t="n">
-        <v>20.64900068304101</v>
+        <v>25.44658324434771</v>
       </c>
       <c r="H18" t="n">
-        <v>37.44944201252041</v>
+        <v>37.85571026013244</v>
       </c>
       <c r="I18" t="n">
-        <v>1.803099939854928</v>
+        <v>1.964067181079711</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739725570746059</v>
+        <v>4.690775683088686</v>
       </c>
       <c r="K18" t="n">
-        <v>21.62973779276417</v>
+        <v>15.31061070213211</v>
       </c>
       <c r="L18" t="n">
-        <v>43.95855504693084</v>
+        <v>44.4761709392337</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93994272749592</v>
+        <v>99.93458166543267</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.34802722766587</v>
+        <v>81.76583299191427</v>
       </c>
       <c r="C19" t="n">
-        <v>33.59786312226068</v>
+        <v>37.52806697609672</v>
       </c>
       <c r="D19" t="n">
-        <v>1.156493063481887</v>
+        <v>1.350683529016928</v>
       </c>
       <c r="E19" t="n">
-        <v>11.67615813738693</v>
+        <v>11.87593133816554</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758850114132062</v>
+        <v>0.7510252232474175</v>
       </c>
       <c r="G19" t="n">
-        <v>20.02824876911073</v>
+        <v>23.57548382623211</v>
       </c>
       <c r="H19" t="n">
-        <v>37.47383804347285</v>
+        <v>37.88098596331876</v>
       </c>
       <c r="I19" t="n">
-        <v>1.511625886756036</v>
+        <v>1.637815466637152</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742813213325388</v>
+        <v>4.69390764529636</v>
       </c>
       <c r="K19" t="n">
-        <v>22.65197277233413</v>
+        <v>18.23416700808573</v>
       </c>
       <c r="L19" t="n">
-        <v>43.6998093788846</v>
+        <v>44.18320859412088</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9496452734794</v>
+        <v>99.94544257830334</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.65344393877373</v>
+        <v>78.70081665925574</v>
       </c>
       <c r="C20" t="n">
-        <v>31.1351148350467</v>
+        <v>34.71558195436972</v>
       </c>
       <c r="D20" t="n">
-        <v>1.062258480472026</v>
+        <v>1.23890973749835</v>
       </c>
       <c r="E20" t="n">
-        <v>10.93481534479755</v>
+        <v>11.12076237908897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592771774976367</v>
+        <v>0.7514596223088161</v>
       </c>
       <c r="G20" t="n">
-        <v>18.39628595777091</v>
+        <v>21.62452998876227</v>
       </c>
       <c r="H20" t="n">
-        <v>37.49492745638563</v>
+        <v>37.90289663187949</v>
       </c>
       <c r="I20" t="n">
-        <v>1.260397162489746</v>
+        <v>1.365635660287752</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74548235936023</v>
+        <v>4.696622639430101</v>
       </c>
       <c r="K20" t="n">
-        <v>25.34655606122626</v>
+        <v>21.29918334074427</v>
       </c>
       <c r="L20" t="n">
-        <v>43.4763394957616</v>
+        <v>43.93973983081274</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95801039203457</v>
+        <v>99.95450512592674</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.3122557350752</v>
+        <v>75.75361986858387</v>
       </c>
       <c r="C21" t="n">
-        <v>35.29234687153262</v>
+        <v>31.97813655647094</v>
       </c>
       <c r="D21" t="n">
-        <v>1.063042732342763</v>
+        <v>1.132035198375735</v>
       </c>
       <c r="E21" t="n">
-        <v>13.16435098236493</v>
+        <v>10.35119654356136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598377421415602</v>
+        <v>0.7518361111763873</v>
       </c>
       <c r="G21" t="n">
-        <v>20.33117130368356</v>
+        <v>19.75909007305153</v>
       </c>
       <c r="H21" t="n">
-        <v>39.44391308542068</v>
+        <v>37.92188636626702</v>
       </c>
       <c r="I21" t="n">
-        <v>1.800954000736931</v>
+        <v>1.13859988129941</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748985888384753</v>
+        <v>4.698975694852421</v>
       </c>
       <c r="K21" t="n">
-        <v>18.6877442649248</v>
+        <v>24.24638013141615</v>
       </c>
       <c r="L21" t="n">
-        <v>45.95992135153207</v>
+        <v>43.73754898821605</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94001248798949</v>
+        <v>99.96206567610312</v>
       </c>
     </row>
   </sheetData>
